--- a/results/andar_할인율모니터링_20260906.xlsx
+++ b/results/andar_할인율모니터링_20260906.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,7 +571,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3,535</t>
+          <t>3,536</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3,535</t>
+          <t>3,536</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>10,055</t>
+          <t>10,060</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>8,025</t>
+          <t>8,031</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1247,126 +1247,126 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8817&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9620&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EMTSC-03</t>
+          <t>EMTBG-12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 풀 토삭스 (HOLE)</t>
+          <t>데일리 쇼퍼백</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17,800</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4,816</t>
+          <t>1,401</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9620&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8817&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EMTBG-12</t>
+          <t>EMTSC-03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>데일리 쇼퍼백</t>
+          <t>[1&amp;1] 논슬립 서포트 풀 토삭스 (HOLE)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>17,800</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1,401</t>
+          <t>4,816</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15403&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EPTSC-04</t>
+          <t>EOTBG-21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[3 SET] 필라테스 삭스</t>
+          <t>데일리 라운드백</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>41,700</t>
+          <t>75,000</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>30,900</t>
+          <t>49,500</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EPTSC-05</t>
+          <t>EPTSC-04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EPTSC-06</t>
+          <t>EPTSC-05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1457,101 +1457,101 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15403&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EOTBG-21</t>
+          <t>EPTSC-06</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>데일리 라운드백</t>
+          <t>[3 SET] 필라테스 삭스</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>41,700</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>49,500</t>
+          <t>30,900</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>385</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16868&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ENTBG-03</t>
+          <t>EPTBG-03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>데일리 스트링 쇼퍼백</t>
+          <t>컴팩트 포켓 크로스백</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>40,500</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13862&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EOTBG-03</t>
+          <t>ENTBG-03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>데이 앤 트래블 숄더백</t>
+          <t>데일리 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1561,17 +1561,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>53,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>725</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1583,163 +1583,163 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13838&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13862&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EOTFB-01</t>
+          <t>EOTBG-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>에어쿨링 서스테이너블 와이드 헤드밴드</t>
+          <t>데이 앤 트래블 숄더백</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>53,000</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2,389</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16868&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10478&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EPTBG-03</t>
+          <t>ENTBG-05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>컴팩트 포켓 크로스백</t>
+          <t>미니 숄더 앤 크로스백</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>40,500</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>5,112</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10478&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12318&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ENTBG-05</t>
+          <t>ENTBG-13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>미니 숄더 앤 크로스백</t>
+          <t>데일리 스퀘어백</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5,112</t>
+          <t>428</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12318&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13838&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ENTBG-13</t>
+          <t>EOTFB-01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>데일리 스퀘어백</t>
+          <t>에어쿨링 서스테이너블 와이드 헤드밴드</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>2,395</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1751,37 +1751,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15372&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>EOTBG-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
+          <t>폴더블 미니백 2.0</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15,800</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3,187</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1793,121 +1793,121 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13409&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>EOTBG-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
+          <t>에어플라이 투웨이 프리런 백 3.0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>15,800</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3,187</t>
+          <t>1,137</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EJFST-02</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>릴렉스 요가링</t>
+          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>15,800</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>6,578</t>
+          <t>3,188</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15372&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EOTBG-16</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>폴더블 미니백 2.0</t>
+          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>15,800</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>3,188</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1919,163 +1919,163 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13409&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EOTBG-10</t>
+          <t>EJFST-02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>에어플라이 투웨이 프리런 백 3.0</t>
+          <t>릴렉스 요가링</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1,136</t>
+          <t>6,579</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17414&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15369&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EPTBG-01</t>
+          <t>EOTBG-19</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>에어플라이 프리런 러닝 벨트</t>
+          <t>위켄드 호보백</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>53,000</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17414&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EOTBG-20</t>
+          <t>EPTBG-01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>클라우드 스트링 쇼퍼백</t>
+          <t>에어플라이 프리런 러닝 벨트</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>58,500</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15369&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16629&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EOTBG-19</t>
+          <t>EPTET-01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>위켄드 호보백</t>
+          <t>언더웨어 파우치</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>53,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>337</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2087,42 +2087,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16629&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EPTET-01</t>
+          <t>EOTBG-20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>언더웨어 파우치</t>
+          <t>클라우드 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>58,500</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -2213,294 +2213,294 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15371&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15143&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EOTBG-15</t>
+          <t>EOTBG-17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>폴더블 짐백 2.0</t>
+          <t>3 in 1 캐리온 더플백</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>109,000</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>40,500</t>
+          <t>76,500</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8838&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17437&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EMTSV-03</t>
+          <t>EPTCP-03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 무릎 보호대</t>
+          <t>썬가드 와이드 버킷햇</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15143&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15371&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EOTBG-17</t>
+          <t>EOTBG-15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3 in 1 캐리온 더플백</t>
+          <t>폴더블 짐백 2.0</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>109,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>76,500</t>
+          <t>40,500</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17425&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8838&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EPTSC-06</t>
+          <t>EMTSV-03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>필라테스 크루 삭스</t>
+          <t>[1&amp;1] 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>2,001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16844&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15370&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EPTET-02</t>
+          <t>EOTBG-14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>언더웨어 세탁망</t>
+          <t>폴더블 캐리백 2.0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>49,500</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17425&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>EPTSC-06</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
+          <t>필라테스 크루 삭스</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>79</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15370&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16844&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EOTBG-14</t>
+          <t>EPTET-02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>폴더블 캐리백 2.0</t>
+          <t>언더웨어 세탁망</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>49,500</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>288</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -2549,37 +2549,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5144&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EJPMS-05</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>릴렉스 마사지 스틱 Ⅱ</t>
+          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>10,358</t>
+          <t>672</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2591,27 +2591,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17437&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15629&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EPTCP-03</t>
+          <t>EOTBG-23</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>썬가드 와이드 버킷햇</t>
+          <t>안다르 실버 리유저블백 M</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>365</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -2675,69 +2675,69 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11962&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11027&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ENTMT-01</t>
+          <t>ENTSC-08</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>레스트 인 마블 요가매트 (4mm)</t>
+          <t>[5 SET] 에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>811</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6660&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13852&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EKPMT-03</t>
+          <t>EOTET-03</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>릴렉스 논슬립 요가 타월</t>
+          <t>라이트 러닝 베스트</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>35,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>35,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2747,49 +2747,49 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1,556</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11027&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5144&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ENTSC-08</t>
+          <t>EJPMS-05</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[5 SET] 에어컴피 크루 삭스</t>
+          <t>릴렉스 마사지 스틱 Ⅱ</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>10,358</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2927,27 +2927,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15409&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14563&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EOTSC-15</t>
+          <t>EOTMK-01</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 풀 토삭스</t>
+          <t>UV 프로텍션 골프 마스크 (벨크로)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2957,39 +2957,39 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>1,099</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11962&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>ENTMT-01</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>맨즈 논슬립 풀 토삭스</t>
+          <t>레스트 인 마블 요가매트 (4mm)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2999,39 +2999,39 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>268</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13852&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EOTET-03</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>라이트 러닝 베스트</t>
+          <t>맨즈 논슬립 풀 토삭스</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3041,39 +3041,39 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5145&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6660&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EJPFR-04</t>
+          <t>EKPMT-03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>릴렉스 폼롤러 Ⅱ</t>
+          <t>릴렉스 논슬립 요가 타월</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>35,900</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>35,900</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>6,362</t>
+          <t>1,557</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3095,27 +3095,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14563&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15409&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EOTMK-01</t>
+          <t>EOTSC-15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UV 프로텍션 골프 마스크 (벨크로)</t>
+          <t>논슬립 퍼포먼스 풀 토삭스</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3125,39 +3125,39 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1,099</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17423&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5145&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EPTSC-04</t>
+          <t>EJPFR-04</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>필라테스 토삭스</t>
+          <t>릴렉스 폼롤러 Ⅱ</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>6,362</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3179,37 +3179,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17423&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EOTSC-16</t>
+          <t>EPTSC-04</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
+          <t>필라테스 토삭스</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>25,800</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>EOTSC-16</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3263,37 +3263,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EMTRB-01</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>서포트 힙 밴드</t>
+          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>25,800</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1,365</t>
+          <t>513</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EMTRB-02</t>
+          <t>EMTRB-01</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1,365</t>
+          <t>1,366</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EMTRB-03</t>
+          <t>EMTRB-02</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1,365</t>
+          <t>1,366</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3389,27 +3389,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5837&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EJFMB-03</t>
+          <t>EMTRB-03</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>릴렉스 짐볼 65cm</t>
+          <t>서포트 힙 밴드</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3419,39 +3419,39 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2,110</t>
+          <t>1,366</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13854&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5837&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EOTSC-06</t>
+          <t>EJFMB-03</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>서포트 쿠션 러닝 삭스</t>
+          <t>릴렉스 짐볼 65cm</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3461,39 +3461,39 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>2,110</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16631&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13854&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EPTSV-03</t>
+          <t>EOTSC-06</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>컴프레션 카프 슬리브 (종아리 보호대)</t>
+          <t>서포트 쿠션 러닝 삭스</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>761</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -3557,27 +3557,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9989&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16631&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EMTET-02</t>
+          <t>EPTSV-03</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>소프트 쿠셔닝 훌라후프</t>
+          <t>컴프레션 카프 슬리브 (종아리 보호대)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3587,39 +3587,39 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14561&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10554&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EOTBG-05</t>
+          <t>ENTMK-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>메쉬 포켓 비치백</t>
+          <t>UV 프로텍션 맨즈 골프 마스크</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>1,535</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3641,27 +3641,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9989&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EOTSV-04</t>
+          <t>EMTET-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>프리런 라이트 러닝 밴드</t>
+          <t>소프트 쿠셔닝 훌라후프</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3671,207 +3671,207 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>622</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ENTSC-19</t>
+          <t>EOTSV-04</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
+          <t>프리런 라이트 러닝 밴드</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16650&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>EPTCP-02</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
+          <t>시그니처 로고 나일론 볼캡</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15377&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EOTGL-04</t>
+          <t>ENTSC-19</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>논슬립 스킨 요기 글러브</t>
+          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>304</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16650&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EPTCP-02</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>시그니처 로고 나일론 볼캡</t>
+          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>304</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10554&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12765&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ENTMK-01</t>
+          <t>ENTBG-16</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>UV 프로텍션 맨즈 골프 마스크</t>
+          <t>라이트 패딩 쇼퍼백</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1,534</t>
+          <t>623</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3893,27 +3893,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13859&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13842&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ENTSO-12</t>
+          <t>EOTBG-04</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>안다르 제트플라이 (맨즈)</t>
+          <t>데님 포켓 숄더백</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3923,39 +3923,39 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12765&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14561&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ENTBG-16</t>
+          <t>EOTBG-05</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>라이트 패딩 쇼퍼백</t>
+          <t>메쉬 포켓 비치백</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3977,27 +3977,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10948&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EKPRB-04</t>
+          <t>ENTSC-20</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
+          <t>시그니처 로고 크루 삭스</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>34,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>34,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4007,39 +4007,39 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>567</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10948&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13859&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ENTSC-20</t>
+          <t>ENTSO-12</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>시그니처 로고 크루 삭스</t>
+          <t>안다르 제트플라이 (맨즈)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4049,39 +4049,39 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>695</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13842&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15377&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EOTBG-04</t>
+          <t>EOTGL-04</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>데님 포켓 숄더백</t>
+          <t>논슬립 스킨 요기 글러브</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4091,39 +4091,39 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>189</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6662&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8621&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EKPMB-02</t>
+          <t>EMTSV-06</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>릴렉스 미니 짐볼</t>
+          <t>에어쿨링 손목 보호대</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4133,39 +4133,39 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1,224</t>
+          <t>1,087</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8578&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EMTSC-01</t>
+          <t>ENTFB-01</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>링글 크루 삭스</t>
+          <t>에어쿨링 라인 스크런치</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1,324</t>
+          <t>763</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4187,69 +4187,69 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EKPET-01</t>
+          <t>EKPRB-04</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
+          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>41,800</t>
+          <t>34,900</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>35,600</t>
+          <t>34,900</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11458&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ENTSC-13</t>
+          <t>EOTSV-03</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 크루삭스</t>
+          <t>서포트 허리 보호대</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>177</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4271,27 +4271,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6662&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EKPMB-01</t>
+          <t>EKPMB-02</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>릴렉스 웨이트볼 0.5kg</t>
+          <t>릴렉스 미니 짐볼</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4301,39 +4301,39 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>1,224</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11458&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>ENTSC-13</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>컴프레션 러닝 니삭스</t>
+          <t>논슬립 퍼포먼스 크루삭스</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4343,39 +4343,39 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>665</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EOTSV-03</t>
+          <t>EKPMB-01</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>서포트 허리 보호대</t>
+          <t>릴렉스 웨이트볼 0.5kg</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>692</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4397,27 +4397,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8578&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ENTFB-01</t>
+          <t>EMTSC-01</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>에어쿨링 라인 스크런치</t>
+          <t>링글 크루 삭스</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>1,324</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4439,37 +4439,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8621&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EMTSV-06</t>
+          <t>ENTSV-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>에어쿨링 손목 보호대</t>
+          <t>[1&amp;1] 3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>25,900</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1,083</t>
+          <t>549</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4481,27 +4481,27 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15153&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EOTSC-13</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>테이핑 테크 러닝 삭스</t>
+          <t>컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4511,39 +4511,39 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>345</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ENTSC-12</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 토삭스</t>
+          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4553,133 +4553,133 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>4,135</t>
+          <t>560</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ENTSV-01</t>
+          <t>EKPET-01</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>[1&amp;1] 3D 쿨링 팔토시</t>
+          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>41,800</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>25,900</t>
+          <t>35,600</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>594</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13404&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10953&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EOTGL-01</t>
+          <t>ENTSC-07</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>짐 글러브 2.0</t>
+          <t>[3 SET] 에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>51,000</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>561</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8837&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16847&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>EPTSC-02</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 발목 보호대</t>
+          <t>하이 쿠션 테이핑 러닝 삭스</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4691,27 +4691,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14562&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>EOTBG-11</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
+          <t>메쉬 파우치</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4721,39 +4721,39 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>190</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16847&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9996&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EPTSC-02</t>
+          <t>EMTSC-27</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>하이 쿠션 테이핑 러닝 삭스</t>
+          <t>올라운드 오버 니삭스</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>295</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4775,27 +4775,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EPTFB-02</t>
+          <t>ENTSC-12</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>퍼포먼스 심리스 손목밴드</t>
+          <t>논슬립 퍼포먼스 토삭스</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4805,49 +4805,49 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>4,135</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14562&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8837&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EOTBG-11</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>메쉬 파우치</t>
+          <t>[1&amp;1] 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>715</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4859,69 +4859,69 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10953&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15153&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ENTSC-07</t>
+          <t>EOTSC-13</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>[3 SET] 에어컴피 크루 삭스</t>
+          <t>테이핑 테크 러닝 삭스</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>51,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>272</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17424&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17440&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EPTSC-05</t>
+          <t>EPTET-03</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>필라테스 앵클 삭스</t>
+          <t>안다르 3단 양우산</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4931,39 +4931,39 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17440&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EPTET-03</t>
+          <t>EPTFB-02</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>안다르 3단 양우산</t>
+          <t>퍼포먼스 심리스 손목밴드</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4973,39 +4973,39 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13404&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EOTSC-16</t>
+          <t>EOTGL-01</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>논슬립 스킨 하프 토삭스</t>
+          <t>짐 글러브 2.0</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5015,29 +5015,29 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>286</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9996&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17424&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EMTSC-27</t>
+          <t>EPTSC-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>올라운드 오버 니삭스</t>
+          <t>필라테스 앵클 삭스</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5057,39 +5057,39 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15144&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16660&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EOTBO-01</t>
+          <t>EOTET-03</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>액티브 스포츠 보틀 (650ml)</t>
+          <t>맨즈 라이트 러닝 베스트</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5099,54 +5099,54 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15144&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EPTSC-07</t>
+          <t>EOTBO-01</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
+          <t>액티브 스포츠 보틀 (650ml)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EPTSC-08</t>
+          <t>EPTSC-07</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5195,42 +5195,42 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16660&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EOTET-03</t>
+          <t>EPTSC-08</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>맨즈 라이트 러닝 베스트</t>
+          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -5279,27 +5279,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EOTSC-10</t>
+          <t>EOTSC-16</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>시그니처 로고 맨즈 크루 삭스</t>
+          <t>논슬립 스킨 하프 토삭스</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -5363,37 +5363,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13605&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EOTSV-02</t>
+          <t>EOTSC-10</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 팔꿈치 보호대</t>
+          <t>시그니처 로고 맨즈 크루 삭스</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5405,69 +5405,69 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13605&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>EOTSV-02</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>서포트 발목 보호대</t>
+          <t>[1&amp;1] 하이 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11459&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12096&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ENTSC-14</t>
+          <t>ENTET-02</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 니삭스</t>
+          <t>릴렉스 소프트 웨이트바 2kg</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5477,39 +5477,39 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EOTSV-01</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>하이 서포트 무릎 보호대</t>
+          <t>서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>715</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5531,27 +5531,27 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EOTSC-05</t>
+          <t>EOTSV-01</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>올데이 수피마 앵클 삭스</t>
+          <t>하이 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>703</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5573,27 +5573,27 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15629&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EOTBG-23</t>
+          <t>EOTSC-05</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>안다르 실버 리유저블백 M</t>
+          <t>올데이 수피마 앵클 삭스</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>473</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5615,27 +5615,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17415&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EPTSC-01</t>
+          <t>EOTCP-03</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>쿨 메쉬 서포트 러닝 삭스</t>
+          <t>쿨 라운드 볼캡</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5645,49 +5645,49 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13805&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17857&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EOTSC-04</t>
+          <t>EPTSC-03</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>올데이 수피마 스니커즈 삭스</t>
+          <t>[1&amp;1] 데일리 루즈 삭스</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>18,900</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5699,27 +5699,27 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16031&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13805&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EOTGL-02</t>
+          <t>EOTSC-04</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>히트 런 글러브</t>
+          <t>올데이 수피마 스니커즈 삭스</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5729,49 +5729,49 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>427</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17415&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EMTSC-28</t>
+          <t>EPTSC-01</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
+          <t>쿨 메쉬 서포트 러닝 삭스</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5783,27 +5783,27 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8770&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16031&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EMTSV-03</t>
+          <t>EOTGL-02</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>서포트 무릎 보호대</t>
+          <t>히트 런 글러브</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5813,81 +5813,81 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>EMTSC-28</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
+          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>395</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12096&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ENTET-02</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>릴렉스 소프트 웨이트바 2kg</t>
+          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5897,39 +5897,39 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>643</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11459&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>ENTSC-14</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>논슬립 스킨 토삭스</t>
+          <t>논슬립 퍼포먼스 니삭스</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5939,81 +5939,81 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>752</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17857&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>EPTSC-03</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>[1&amp;1] 데일리 루즈 삭스</t>
+          <t>논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>18,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13406&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EOTCP-03</t>
+          <t>EOTSV-02</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>쿨 라운드 볼캡</t>
+          <t>하이 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6077,37 +6077,37 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13406&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EOTSV-02</t>
+          <t>EOTSC-18</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>하이 서포트 팔꿈치 보호대</t>
+          <t>[1&amp;1] 올데이 기모 삭스</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6119,27 +6119,27 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16033&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8770&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EOTMK-02</t>
+          <t>EMTSV-03</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>소프텐션 넥마스크</t>
+          <t>서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6149,81 +6149,81 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>2,001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11963&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EOTSC-18</t>
+          <t>ENTSC-19</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>[1&amp;1] 올데이 기모 삭스</t>
+          <t>맨즈 논슬립 하프 토삭스</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11963&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16033&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ENTSC-19</t>
+          <t>EOTMK-02</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>맨즈 논슬립 하프 토삭스</t>
+          <t>소프텐션 넥마스크</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6233,39 +6233,39 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>157</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11061&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6666&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ENTSV-01</t>
+          <t>EKPET-01</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>3D 쿨링 팔토시</t>
+          <t>릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6275,39 +6275,39 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>594</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12778&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ENTBG-14</t>
+          <t>EOTSC-01</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>웨이브 패딩 파우치</t>
+          <t>프레시 필드 니삭스</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>295</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6329,17 +6329,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11061&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>EOTSC-01</t>
+          <t>ENTSV-01</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>프레시 필드 니삭스</t>
+          <t>3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6359,39 +6359,39 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>549</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6666&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12778&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>EKPET-01</t>
+          <t>ENTBG-14</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>릴렉스 소프트 웨이트바 1kg</t>
+          <t>웨이브 패딩 파우치</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>191</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6413,59 +6413,59 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17387&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10191&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>EPTSC-08</t>
+          <t>EMTSC-26</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>맨즈 필라테스 크루 삭스</t>
+          <t>[1&amp;1] 램스울 크루 삭스</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>840</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17387&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EPTSC-07</t>
+          <t>EPTSC-08</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>맨즈 필라테스 앵클 삭스</t>
+          <t>맨즈 필라테스 크루 삭스</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6539,37 +6539,37 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10191&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12793&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EMTSC-26</t>
+          <t>ENTMU-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>[1&amp;1] 램스울 크루 삭스</t>
+          <t>소프트 니트 머플러</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>472</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6581,27 +6581,27 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16640&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EPTBG-05</t>
+          <t>ENTSC-24</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>안다르 시그니처 로고 에코백</t>
+          <t>웜 슬릿 레그 워머</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6611,39 +6611,39 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11725&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8768&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ENTFB-04</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>더블 링글 손목밴드</t>
+          <t>서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6653,39 +6653,39 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>589</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11725&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ENTSC-24</t>
+          <t>ENTFB-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>웜 슬릿 레그 워머</t>
+          <t>더블 링글 손목밴드</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6695,39 +6695,39 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>433</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8768&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12783&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>ENTSC-26</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>서포트 팔꿈치 보호대</t>
+          <t>니트 기모 오버 니삭스</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>354</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -6791,27 +6791,27 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12795&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ENTCP-05</t>
+          <t>EOTCP-06</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>소프트 니트 비니</t>
+          <t>소프트 니트 버킷햇</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6821,39 +6821,39 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12793&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ENTMU-01</t>
+          <t>EPTSC-07</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>소프트 니트 머플러</t>
+          <t>맨즈 필라테스 앵클 삭스</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6863,81 +6863,81 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10939&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12795&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ENTSC-07</t>
+          <t>ENTCP-05</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>에어컴피 크루 삭스</t>
+          <t>소프트 니트 비니</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>361</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17436&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16640&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EPTSV-01</t>
+          <t>EPTBG-05</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>3D 쿨링 핑거홀 팔토시</t>
+          <t>안다르 시그니처 로고 에코백</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6947,81 +6947,81 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.2</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9988&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10939&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EMTSC-26</t>
+          <t>ENTSC-07</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>램스울 크루 삭스</t>
+          <t>에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>561</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17436&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EOTSC-20</t>
+          <t>EPTSV-01</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>레그 미들 워머</t>
+          <t>3D 쿨링 핑거홀 팔토시</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -7211,27 +7211,27 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12783&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16035&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ENTSC-26</t>
+          <t>EOTSC-12</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>니트 기모 오버 니삭스</t>
+          <t>소프트 니트 기모 니삭스</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7241,29 +7241,29 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16035&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12794&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EOTSC-12</t>
+          <t>ENTFB-05</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>소프트 니트 기모 니삭스</t>
+          <t>소프트 니트 헤드밴드</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7283,39 +7283,39 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>913</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12794&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ENTFB-05</t>
+          <t>EOTSC-20</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>소프트 니트 헤드밴드</t>
+          <t>레그 미들 워머</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -7463,27 +7463,27 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16034&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>EOTCP-06</t>
+          <t>EOTGL-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>소프트 니트 버킷햇</t>
+          <t>소프트 니트 플립 글러브</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7493,39 +7493,39 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16034&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16032&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>EOTGL-03</t>
+          <t>EOTCP-05</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>소프트 니트 플립 글러브</t>
+          <t>히트 런 이어플랩 캡</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7535,39 +7535,39 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16032&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15733&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>EOTCP-05</t>
+          <t>EOTSC-19</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>히트 런 이어플랩 캡</t>
+          <t>레그 숏 워머</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7589,27 +7589,27 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15733&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13831&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>EOTSC-19</t>
+          <t>EOTCP-02</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>레그 숏 워머</t>
+          <t>데님 로고 볼캡</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -7631,27 +7631,27 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13831&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12792&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>EOTCP-02</t>
+          <t>ENTGL-05</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>데님 로고 볼캡</t>
+          <t>니트 글러브</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -7661,39 +7661,39 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>371</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12792&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12488&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ENTGL-05</t>
+          <t>ENTBG-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>니트 글러브</t>
+          <t>스퀘어 크로스백</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7703,39 +7703,39 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>630</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12488&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11092&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ENTBG-10</t>
+          <t>ENTSC-05</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>스퀘어 크로스백</t>
+          <t>에어프레시 크루 삭스</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>575</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -7757,27 +7757,27 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11092&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9993&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ENTSC-05</t>
+          <t>EMTSC-29</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>에어프레시 크루 삭스</t>
+          <t>니트 루즈 삭스</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>513</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -7799,17 +7799,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9993&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9988&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>EMTSC-29</t>
+          <t>EMTSC-26</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>니트 루즈 삭스</t>
+          <t>램스울 크루 삭스</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -7829,10 +7829,94 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>332</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=8799&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>EMTFB-01</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>[3 SET] 에어쿨링 스크런치</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>17,700</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>13,900</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>1,639</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=8799&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>ENTFB-02</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>[3 SET] 에어쿨링 스크런치</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>17,700</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>13,900</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>1,639</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
